--- a/DXLibProject_Start/Data/CSV/KeyCode.xlsx
+++ b/DXLibProject_Start/Data/CSV/KeyCode.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7652614-DAC1-4B74-AF77-70E15347FE11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFA7A17C-4163-48AB-81AD-F7E825EA86A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1815" yWindow="1815" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KeyCode" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="73">
   <si>
     <t>GpUp</t>
   </si>
@@ -279,6 +279,10 @@
   </si>
   <si>
     <t>UseItem</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PickUpItem</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1148,7 +1152,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C62AA4DB-6C78-44DC-A30A-4C66BF09A693}">
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="16.125" bestFit="1" customWidth="1"/>
@@ -1460,7 +1464,7 @@
         <v>40</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>42</v>
@@ -1479,7 +1483,7 @@
       </c>
       <c r="I7" s="2">
         <f>VLOOKUP(C7,KeyCode!A:B,2,FALSE)</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J7" s="2">
         <f>VLOOKUP(D7,KeyCode!A:B,2,FALSE)</f>
@@ -2049,6 +2053,56 @@
       </c>
       <c r="N18" s="2">
         <f>VLOOKUP(H17,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" s="3">
+        <v>17</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I19" s="2">
+        <f>VLOOKUP(C19,KeyCode!A:B,2,FALSE)</f>
+        <v>6</v>
+      </c>
+      <c r="J19" s="2">
+        <f>VLOOKUP(D19,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="2">
+        <f>VLOOKUP(E19,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="2">
+        <f>VLOOKUP(F18,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="M19" s="2">
+        <f>VLOOKUP(G18,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="N19" s="2">
+        <f>VLOOKUP(H18,KeyCode!A:B,2,FALSE)</f>
         <v>0</v>
       </c>
     </row>
@@ -2063,7 +2117,7 @@
           <x14:formula1>
             <xm:f>KeyCode!$A$2:$A$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:H18</xm:sqref>
+          <xm:sqref>C2:H19</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/DXLibProject_Start/Data/CSV/KeyCode.xlsx
+++ b/DXLibProject_Start/Data/CSV/KeyCode.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFA7A17C-4163-48AB-81AD-F7E825EA86A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9664323D-05B2-4F18-90CB-FA81F1E6126F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1815" yWindow="1815" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4050" yWindow="-13485" windowWidth="21585" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KeyCode" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="189">
   <si>
     <t>GpUp</t>
   </si>
@@ -68,37 +68,10 @@
     <t>GpStart</t>
   </si>
   <si>
-    <t>GpBack</t>
-  </si>
-  <si>
-    <t>GpLeftShoulder</t>
-  </si>
-  <si>
-    <t>GpRightShoulder</t>
-  </si>
-  <si>
-    <t>GpLeftTrigger</t>
-  </si>
-  <si>
     <t>GpRightTrigger</t>
   </si>
   <si>
     <t>GpLeftThumb</t>
-  </si>
-  <si>
-    <t>GpRightThumb</t>
-  </si>
-  <si>
-    <t>GpRightThumbUp</t>
-  </si>
-  <si>
-    <t>GpRightThumbRight</t>
-  </si>
-  <si>
-    <t>GpRightThumbDown</t>
-  </si>
-  <si>
-    <t>GpRightThumbLeft</t>
   </si>
   <si>
     <t>GpLeftThumbUp</t>
@@ -236,10 +209,6 @@
   </si>
   <si>
     <t>GpCross</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>GpCross</t>
   </si>
   <si>
     <t>DragonCall</t>
@@ -257,14 +226,6 @@
   </si>
   <si>
     <t>GpLeftVector</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>GpRightVector</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>GpLeftVector</t>
   </si>
   <si>
     <t>GpRightVector</t>
@@ -284,13 +245,402 @@
   <si>
     <t>PickUpItem</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>KeyBoard_Back</t>
+  </si>
+  <si>
+    <t>KeyBoard_Tab</t>
+  </si>
+  <si>
+    <t>KeyBoard_Return</t>
+  </si>
+  <si>
+    <t>KeyBoard_LShift</t>
+  </si>
+  <si>
+    <t>KeyBoard_RShift</t>
+  </si>
+  <si>
+    <t>KeyBoard_LControl</t>
+  </si>
+  <si>
+    <t>KeyBoard_RControl</t>
+  </si>
+  <si>
+    <t>KeyBoard_Escape</t>
+  </si>
+  <si>
+    <t>KeyBoard_Space</t>
+  </si>
+  <si>
+    <t>KeyBoard_PGUp</t>
+  </si>
+  <si>
+    <t>KeyBoard_PGDown</t>
+  </si>
+  <si>
+    <t>KeyBoard_End</t>
+  </si>
+  <si>
+    <t>KeyBoard_Home</t>
+  </si>
+  <si>
+    <t>KeyBoard_Left</t>
+  </si>
+  <si>
+    <t>KeyBoard_Up</t>
+  </si>
+  <si>
+    <t>KeyBoard_Right</t>
+  </si>
+  <si>
+    <t>KeyBoard_Down</t>
+  </si>
+  <si>
+    <t>KeyBoard_Insert</t>
+  </si>
+  <si>
+    <t>KeyBoard_Delete</t>
+  </si>
+  <si>
+    <t>KeyBoard_Minus</t>
+  </si>
+  <si>
+    <t>KeyBoard_Yen</t>
+  </si>
+  <si>
+    <t>KeyBoard_Prevtrack</t>
+  </si>
+  <si>
+    <t>KeyBoard_Period</t>
+  </si>
+  <si>
+    <t>KeyBoard_Slash</t>
+  </si>
+  <si>
+    <t>KeyBoard_LAlt</t>
+  </si>
+  <si>
+    <t>KeyBoard_RAlt</t>
+  </si>
+  <si>
+    <t>KeyBoard_Scroll</t>
+  </si>
+  <si>
+    <t>KeyBoard_Semicolon</t>
+  </si>
+  <si>
+    <t>KeyBoard_Colon</t>
+  </si>
+  <si>
+    <t>KeyBoard_LBracket</t>
+  </si>
+  <si>
+    <t>KeyBoard_RBracket</t>
+  </si>
+  <si>
+    <t>KeyBoard_At</t>
+  </si>
+  <si>
+    <t>KeyBoard_BackSlash</t>
+  </si>
+  <si>
+    <t>KeyBoard_Comma</t>
+  </si>
+  <si>
+    <t>KeyBoard_CapsLock</t>
+  </si>
+  <si>
+    <t>KeyBoard_Pause</t>
+  </si>
+  <si>
+    <t>KeyBoard_NumPad0</t>
+  </si>
+  <si>
+    <t>KeyBoard_NumPad1</t>
+  </si>
+  <si>
+    <t>KeyBoard_NumPad2</t>
+  </si>
+  <si>
+    <t>KeyBoard_NumPad3</t>
+  </si>
+  <si>
+    <t>KeyBoard_NumPad4</t>
+  </si>
+  <si>
+    <t>KeyBoard_NumPad5</t>
+  </si>
+  <si>
+    <t>KeyBoard_NumPad6</t>
+  </si>
+  <si>
+    <t>KeyBoard_NumPad7</t>
+  </si>
+  <si>
+    <t>KeyBoard_NumPad8</t>
+  </si>
+  <si>
+    <t>KeyBoard_NumPad9</t>
+  </si>
+  <si>
+    <t>KeyBoard_Multiply</t>
+  </si>
+  <si>
+    <t>KeyBoard_Add</t>
+  </si>
+  <si>
+    <t>KeyBoard_Subtract</t>
+  </si>
+  <si>
+    <t>KeyBoard_DecimalECIMAL</t>
+  </si>
+  <si>
+    <t>KeyBoard_Divide</t>
+  </si>
+  <si>
+    <t>KeyBoard_NumPadEnter</t>
+  </si>
+  <si>
+    <t>KeyBoard_F1</t>
+  </si>
+  <si>
+    <t>KeyBoard_F2</t>
+  </si>
+  <si>
+    <t>KeyBoard_F3</t>
+  </si>
+  <si>
+    <t>KeyBoard_F4</t>
+  </si>
+  <si>
+    <t>KeyBoard_F5</t>
+  </si>
+  <si>
+    <t>KeyBoard_F6</t>
+  </si>
+  <si>
+    <t>KeyBoard_F7</t>
+  </si>
+  <si>
+    <t>KeyBoard_F8</t>
+  </si>
+  <si>
+    <t>KeyBoard_F9</t>
+  </si>
+  <si>
+    <t>KeyBoard_F10</t>
+  </si>
+  <si>
+    <t>KeyBoard_F11</t>
+  </si>
+  <si>
+    <t>KeyBoard_F12</t>
+  </si>
+  <si>
+    <t>KeyBoard_A</t>
+  </si>
+  <si>
+    <t>KeyBoard_B</t>
+  </si>
+  <si>
+    <t>KeyBoard_C</t>
+  </si>
+  <si>
+    <t>KeyBoard_D</t>
+  </si>
+  <si>
+    <t>KeyBoard_E</t>
+  </si>
+  <si>
+    <t>KeyBoard_F</t>
+  </si>
+  <si>
+    <t>KeyBoard_G</t>
+  </si>
+  <si>
+    <t>KeyBoard_H</t>
+  </si>
+  <si>
+    <t>KeyBoard_I</t>
+  </si>
+  <si>
+    <t>KeyBoard_J</t>
+  </si>
+  <si>
+    <t>KeyBoard_K</t>
+  </si>
+  <si>
+    <t>KeyBoard_L</t>
+  </si>
+  <si>
+    <t>KeyBoard_M</t>
+  </si>
+  <si>
+    <t>KeyBoard_N</t>
+  </si>
+  <si>
+    <t>KeyBoard_O</t>
+  </si>
+  <si>
+    <t>KeyBoard_P</t>
+  </si>
+  <si>
+    <t>KeyBoard_Q</t>
+  </si>
+  <si>
+    <t>KeyBoard_R</t>
+  </si>
+  <si>
+    <t>KeyBoard_S</t>
+  </si>
+  <si>
+    <t>KeyBoard_T</t>
+  </si>
+  <si>
+    <t>KeyBoard_U</t>
+  </si>
+  <si>
+    <t>KeyBoard_V</t>
+  </si>
+  <si>
+    <t>KeyBoard_W</t>
+  </si>
+  <si>
+    <t>KeyBoard_X</t>
+  </si>
+  <si>
+    <t>KeyBoard_Y</t>
+  </si>
+  <si>
+    <t>KeyBoard_Z</t>
+  </si>
+  <si>
+    <t>KeyBoard_0</t>
+  </si>
+  <si>
+    <t>KeyBoard_1</t>
+  </si>
+  <si>
+    <t>KeyBoard_2</t>
+  </si>
+  <si>
+    <t>KeyBoard_3</t>
+  </si>
+  <si>
+    <t>KeyBoard_4</t>
+  </si>
+  <si>
+    <t>KeyBoard_5</t>
+  </si>
+  <si>
+    <t>KeyBoard_6</t>
+  </si>
+  <si>
+    <t>KeyBoard_7</t>
+  </si>
+  <si>
+    <t>KeyBoard_8</t>
+  </si>
+  <si>
+    <t>KeyBoard_9</t>
+  </si>
+  <si>
+    <t>Keyboard</t>
+  </si>
+  <si>
+    <t>Gp_Up</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Gp_Right</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Gp_Down</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Gp_Left</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Gp_North</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Gp_East</t>
+  </si>
+  <si>
+    <t>Gp_South</t>
+  </si>
+  <si>
+    <t>Gp_West</t>
+  </si>
+  <si>
+    <t>Gp_Start</t>
+  </si>
+  <si>
+    <t>Gp_Back</t>
+  </si>
+  <si>
+    <t>Gp_LeftShoulder</t>
+  </si>
+  <si>
+    <t>Gp_RightShoulder</t>
+  </si>
+  <si>
+    <t>Gp_LeftTrigger</t>
+  </si>
+  <si>
+    <t>Gp_RightTrigger</t>
+  </si>
+  <si>
+    <t>Gp_LeftThumb</t>
+  </si>
+  <si>
+    <t>Gp_RightThumb</t>
+  </si>
+  <si>
+    <t>Gp_LeftThumbUp</t>
+  </si>
+  <si>
+    <t>Gp_LeftThumbRight</t>
+  </si>
+  <si>
+    <t>Gp_LeftThumbDown</t>
+  </si>
+  <si>
+    <t>Gp_LeftThumbLeft</t>
+  </si>
+  <si>
+    <t>Gp_RightThumbUp</t>
+  </si>
+  <si>
+    <t>Gp_RightThumbRight</t>
+  </si>
+  <si>
+    <t>Gp_RightThumbDown</t>
+  </si>
+  <si>
+    <t>Gp_RightThumbLeft</t>
+  </si>
+  <si>
+    <t>Gp_Cross</t>
+  </si>
+  <si>
+    <t>Gp_LeftVector</t>
+  </si>
+  <si>
+    <t>Gp_RightVector</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -300,6 +650,26 @@
     </font>
     <font>
       <sz val="6"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
@@ -341,13 +711,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -630,506 +1009,2362 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <dimension ref="A1:E138"/>
+  <sheetFormatPr defaultRowHeight="18.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.25" customWidth="1"/>
     <col min="5" max="5" width="23.25" customWidth="1"/>
+    <col min="8" max="8" width="18.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="18.75" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D2" s="1">
+        <f>VLOOKUP(C2,Device!A:B,2,FALSE)</f>
         <v>-1</v>
       </c>
       <c r="E2" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" ht="18.75" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D3" s="1">
+        <f>VLOOKUP(C3,Device!A:B,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" ht="18.75" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>1</v>
+        <v>163</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D4" s="1">
+        <f>VLOOKUP(C4,Device!A:B,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" ht="18.75" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>2</v>
+        <v>164</v>
       </c>
       <c r="B5" s="1">
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D5" s="1">
+        <f>VLOOKUP(C5,Device!A:B,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" ht="18.75" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>3</v>
+        <v>165</v>
       </c>
       <c r="B6" s="1">
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D6" s="1">
+        <f>VLOOKUP(C6,Device!A:B,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" ht="18.75" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>166</v>
       </c>
       <c r="B7" s="1">
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D7" s="1">
+        <f>VLOOKUP(C7,Device!A:B,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E7" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" ht="18.75" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>167</v>
       </c>
       <c r="B8" s="1">
         <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D8" s="1">
+        <f>VLOOKUP(C8,Device!A:B,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E8" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" ht="18.75" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>168</v>
       </c>
       <c r="B9" s="1">
         <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D9" s="1">
+        <f>VLOOKUP(C9,Device!A:B,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E9" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" ht="18.75" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>7</v>
+        <v>169</v>
       </c>
       <c r="B10" s="1">
         <v>8</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D10" s="1">
+        <f>VLOOKUP(C10,Device!A:B,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E10" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" ht="18.75" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>8</v>
+        <v>170</v>
       </c>
       <c r="B11" s="1">
         <v>9</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D11" s="1">
+        <f>VLOOKUP(C11,Device!A:B,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E11" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" ht="18.75" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>9</v>
+        <v>171</v>
       </c>
       <c r="B12" s="1">
         <v>10</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D12" s="1">
+        <f>VLOOKUP(C12,Device!A:B,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E12" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" ht="18.75" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>10</v>
+        <v>172</v>
       </c>
       <c r="B13" s="1">
         <v>11</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D13" s="1">
+        <f>VLOOKUP(C13,Device!A:B,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E13" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" ht="18.75" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>11</v>
+        <v>173</v>
       </c>
       <c r="B14" s="1">
         <v>12</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D14" s="1">
+        <f>VLOOKUP(C14,Device!A:B,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E14" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" ht="18.75" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>12</v>
+        <v>174</v>
       </c>
       <c r="B15" s="1">
         <v>13</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D15" s="1">
+        <f>VLOOKUP(C15,Device!A:B,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E15" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" ht="18.75" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>13</v>
+        <v>175</v>
       </c>
       <c r="B16" s="1">
         <v>14</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D16" s="1">
+        <f>VLOOKUP(C16,Device!A:B,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E16" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" ht="18.75" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>14</v>
+        <v>176</v>
       </c>
       <c r="B17" s="1">
         <v>15</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D17" s="1">
+        <f>VLOOKUP(C17,Device!A:B,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E17" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" ht="18.75" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>15</v>
+        <v>177</v>
       </c>
       <c r="B18" s="1">
         <v>16</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D18" s="1">
+        <f>VLOOKUP(C18,Device!A:B,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E18" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" ht="18.75" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>20</v>
+        <v>178</v>
       </c>
       <c r="B19" s="1">
         <v>17</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D19" s="1">
+        <f>VLOOKUP(C19,Device!A:B,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E19" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" ht="18.75" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>21</v>
+        <v>179</v>
       </c>
       <c r="B20" s="1">
         <v>18</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D20" s="1">
+        <f>VLOOKUP(C20,Device!A:B,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E20" s="1">
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" ht="18.75" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>22</v>
+        <v>180</v>
       </c>
       <c r="B21" s="1">
         <v>19</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D21" s="1">
+        <f>VLOOKUP(C21,Device!A:B,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E21" s="1">
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" ht="18.75" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>23</v>
+        <v>181</v>
       </c>
       <c r="B22" s="1">
         <v>20</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D22" s="1">
+        <f>VLOOKUP(C22,Device!A:B,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E22" s="1">
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" ht="18.75" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>16</v>
+        <v>182</v>
       </c>
       <c r="B23" s="1">
         <v>21</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D23" s="1">
+        <f>VLOOKUP(C23,Device!A:B,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E23" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" ht="18.75" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>17</v>
+        <v>183</v>
       </c>
       <c r="B24" s="1">
         <v>22</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D24" s="1">
+        <f>VLOOKUP(C24,Device!A:B,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E24" s="1">
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" ht="18.75" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>18</v>
+        <v>184</v>
       </c>
       <c r="B25" s="1">
         <v>23</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D25" s="1">
+        <f>VLOOKUP(C25,Device!A:B,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E25" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" ht="18.75" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>19</v>
+        <v>185</v>
       </c>
       <c r="B26" s="1">
         <v>24</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D26" s="1">
+        <f>VLOOKUP(C26,Device!A:B,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E26" s="1">
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" ht="18.75" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>59</v>
+        <v>186</v>
       </c>
       <c r="B27" s="1">
         <v>25</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D27" s="1">
+        <f>VLOOKUP(C27,Device!A:B,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E27" s="1">
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" ht="18.75" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>65</v>
+        <v>187</v>
       </c>
       <c r="B28" s="1">
         <v>26</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D28" s="1">
+        <f>VLOOKUP(C28,Device!A:B,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E28" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" ht="18.75" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>66</v>
+        <v>188</v>
       </c>
       <c r="B29" s="1">
         <v>27</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D29" s="1">
+        <f>VLOOKUP(C29,Device!A:B,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E29" s="1">
         <v>26</v>
       </c>
+    </row>
+    <row r="30" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A30" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" s="1">
+        <v>28</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D30" s="1">
+        <f>VLOOKUP(C30,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E30" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A31" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" s="1">
+        <v>29</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D31" s="1">
+        <f>VLOOKUP(C31,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E31" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A32" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" s="1">
+        <v>30</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D32" s="1">
+        <f>VLOOKUP(C32,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E32" s="5">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A33" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" s="1">
+        <v>31</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D33" s="1">
+        <f>VLOOKUP(C33,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E33" s="5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A34" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" s="1">
+        <v>32</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D34" s="1">
+        <f>VLOOKUP(C34,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E34" s="5">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A35" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B35" s="1">
+        <v>33</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D35" s="1">
+        <f>VLOOKUP(C35,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E35" s="5">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A36" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B36" s="1">
+        <v>34</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D36" s="1">
+        <f>VLOOKUP(C36,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E36" s="5">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A37" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B37" s="1">
+        <v>35</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D37" s="1">
+        <f>VLOOKUP(C37,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E37" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A38" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B38" s="1">
+        <v>36</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D38" s="1">
+        <f>VLOOKUP(C38,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E38" s="5">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A39" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B39" s="1">
+        <v>37</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D39" s="1">
+        <f>VLOOKUP(C39,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E39" s="5">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A40" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B40" s="1">
+        <v>38</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D40" s="1">
+        <f>VLOOKUP(C40,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E40" s="5">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A41" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B41" s="1">
+        <v>39</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D41" s="1">
+        <f>VLOOKUP(C41,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E41" s="5">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A42" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B42" s="1">
+        <v>40</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D42" s="1">
+        <f>VLOOKUP(C42,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E42" s="5">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A43" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B43" s="1">
+        <v>41</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D43" s="1">
+        <f>VLOOKUP(C43,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E43" s="5">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A44" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B44" s="1">
+        <v>42</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D44" s="1">
+        <f>VLOOKUP(C44,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E44" s="5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A45" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B45" s="1">
+        <v>43</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D45" s="1">
+        <f>VLOOKUP(C45,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E45" s="5">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A46" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B46" s="1">
+        <v>44</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D46" s="1">
+        <f>VLOOKUP(C46,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E46" s="5">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A47" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B47" s="1">
+        <v>45</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D47" s="1">
+        <f>VLOOKUP(C47,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E47" s="5">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A48" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B48" s="1">
+        <v>46</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D48" s="1">
+        <f>VLOOKUP(C48,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E48" s="5">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A49" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B49" s="1">
+        <v>47</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D49" s="1">
+        <f>VLOOKUP(C49,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E49" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A50" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B50" s="1">
+        <v>48</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D50" s="1">
+        <f>VLOOKUP(C50,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E50" s="5">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A51" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B51" s="1">
+        <v>49</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D51" s="1">
+        <f>VLOOKUP(C51,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E51" s="5">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A52" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B52" s="1">
+        <v>50</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D52" s="1">
+        <f>VLOOKUP(C52,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E52" s="5">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A53" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B53" s="1">
+        <v>51</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D53" s="1">
+        <f>VLOOKUP(C53,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E53" s="5">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A54" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B54" s="1">
+        <v>52</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D54" s="1">
+        <f>VLOOKUP(C54,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E54" s="5">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A55" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B55" s="1">
+        <v>53</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D55" s="1">
+        <f>VLOOKUP(C55,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E55" s="5">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A56" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B56" s="1">
+        <v>54</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D56" s="1">
+        <f>VLOOKUP(C56,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E56" s="5">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A57" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B57" s="1">
+        <v>55</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D57" s="1">
+        <f>VLOOKUP(C57,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E57" s="5">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A58" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B58" s="1">
+        <v>56</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D58" s="1">
+        <f>VLOOKUP(C58,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E58" s="5">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A59" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B59" s="1">
+        <v>57</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D59" s="1">
+        <f>VLOOKUP(C59,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E59" s="5">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A60" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B60" s="1">
+        <v>58</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D60" s="1">
+        <f>VLOOKUP(C60,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E60" s="5">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A61" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B61" s="1">
+        <v>59</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D61" s="1">
+        <f>VLOOKUP(C61,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E61" s="5">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A62" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B62" s="1">
+        <v>60</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D62" s="1">
+        <f>VLOOKUP(C62,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E62" s="5">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A63" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B63" s="1">
+        <v>61</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D63" s="1">
+        <f>VLOOKUP(C63,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E63" s="5">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A64" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B64" s="1">
+        <v>62</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D64" s="1">
+        <f>VLOOKUP(C64,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E64" s="5">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A65" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B65" s="1">
+        <v>63</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D65" s="1">
+        <f>VLOOKUP(C65,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E65" s="5">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A66" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B66" s="1">
+        <v>64</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D66" s="1">
+        <f>VLOOKUP(C66,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E66" s="5">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A67" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B67" s="1">
+        <v>65</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D67" s="1">
+        <f>VLOOKUP(C67,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E67" s="5">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A68" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B68" s="1">
+        <v>66</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D68" s="1">
+        <f>VLOOKUP(C68,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E68" s="5">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A69" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B69" s="1">
+        <v>67</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D69" s="1">
+        <f>VLOOKUP(C69,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E69" s="5">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A70" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B70" s="1">
+        <v>68</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D70" s="1">
+        <f>VLOOKUP(C70,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E70" s="5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A71" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B71" s="1">
+        <v>69</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D71" s="1">
+        <f>VLOOKUP(C71,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E71" s="5">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A72" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B72" s="1">
+        <v>70</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D72" s="1">
+        <f>VLOOKUP(C72,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E72" s="5">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A73" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B73" s="1">
+        <v>71</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D73" s="1">
+        <f>VLOOKUP(C73,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E73" s="5">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A74" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B74" s="1">
+        <v>72</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D74" s="1">
+        <f>VLOOKUP(C74,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E74" s="5">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A75" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B75" s="1">
+        <v>73</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D75" s="1">
+        <f>VLOOKUP(C75,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E75" s="5">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A76" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B76" s="1">
+        <v>74</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D76" s="1">
+        <f>VLOOKUP(C76,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E76" s="5">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A77" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B77" s="1">
+        <v>75</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D77" s="1">
+        <f>VLOOKUP(C77,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E77" s="5">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A78" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B78" s="1">
+        <v>76</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D78" s="1">
+        <f>VLOOKUP(C78,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E78" s="5">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A79" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B79" s="1">
+        <v>77</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D79" s="1">
+        <f>VLOOKUP(C79,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E79" s="5">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A80" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B80" s="1">
+        <v>78</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D80" s="1">
+        <f>VLOOKUP(C80,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E80" s="5">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A81" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B81" s="1">
+        <v>79</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D81" s="1">
+        <f>VLOOKUP(C81,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E81" s="5">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A82" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B82" s="1">
+        <v>80</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D82" s="1">
+        <f>VLOOKUP(C82,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E82" s="5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A83" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B83" s="1">
+        <v>81</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D83" s="1">
+        <f>VLOOKUP(C83,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E83" s="5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A84" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B84" s="1">
+        <v>82</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D84" s="1">
+        <f>VLOOKUP(C84,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E84" s="5">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A85" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B85" s="1">
+        <v>83</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D85" s="1">
+        <f>VLOOKUP(C85,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E85" s="5">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A86" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B86" s="1">
+        <v>84</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D86" s="1">
+        <f>VLOOKUP(C86,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E86" s="5">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A87" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B87" s="1">
+        <v>85</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D87" s="1">
+        <f>VLOOKUP(C87,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E87" s="5">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A88" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B88" s="1">
+        <v>86</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D88" s="1">
+        <f>VLOOKUP(C88,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E88" s="5">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A89" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B89" s="1">
+        <v>87</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D89" s="1">
+        <f>VLOOKUP(C89,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E89" s="5">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A90" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B90" s="1">
+        <v>88</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D90" s="1">
+        <f>VLOOKUP(C90,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E90" s="5">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A91" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B91" s="1">
+        <v>89</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D91" s="1">
+        <f>VLOOKUP(C91,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E91" s="5">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A92" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B92" s="1">
+        <v>90</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D92" s="1">
+        <f>VLOOKUP(C92,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E92" s="5">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A93" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B93" s="1">
+        <v>91</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D93" s="1">
+        <f>VLOOKUP(C93,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E93" s="5">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A94" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B94" s="1">
+        <v>92</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D94" s="1">
+        <f>VLOOKUP(C94,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E94" s="5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A95" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B95" s="1">
+        <v>93</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D95" s="1">
+        <f>VLOOKUP(C95,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E95" s="5">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A96" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B96" s="1">
+        <v>94</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D96" s="1">
+        <f>VLOOKUP(C96,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E96" s="5">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A97" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B97" s="1">
+        <v>95</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D97" s="1">
+        <f>VLOOKUP(C97,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E97" s="5">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A98" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B98" s="1">
+        <v>96</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D98" s="1">
+        <f>VLOOKUP(C98,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E98" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A99" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B99" s="1">
+        <v>97</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D99" s="1">
+        <f>VLOOKUP(C99,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E99" s="5">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A100" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B100" s="1">
+        <v>98</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D100" s="1">
+        <f>VLOOKUP(C100,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E100" s="5">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A101" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B101" s="1">
+        <v>99</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D101" s="1">
+        <f>VLOOKUP(C101,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E101" s="5">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A102" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B102" s="1">
+        <v>100</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D102" s="1">
+        <f>VLOOKUP(C102,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E102" s="5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A103" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B103" s="1">
+        <v>101</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D103" s="1">
+        <f>VLOOKUP(C103,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E103" s="5">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A104" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B104" s="1">
+        <v>102</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D104" s="1">
+        <f>VLOOKUP(C104,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E104" s="5">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A105" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B105" s="1">
+        <v>103</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D105" s="1">
+        <f>VLOOKUP(C105,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E105" s="5">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A106" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B106" s="1">
+        <v>104</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D106" s="1">
+        <f>VLOOKUP(C106,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E106" s="5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A107" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B107" s="1">
+        <v>105</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D107" s="1">
+        <f>VLOOKUP(C107,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E107" s="5">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A108" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B108" s="1">
+        <v>106</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D108" s="1">
+        <f>VLOOKUP(C108,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E108" s="5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A109" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B109" s="1">
+        <v>107</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D109" s="1">
+        <f>VLOOKUP(C109,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E109" s="5">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A110" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B110" s="1">
+        <v>108</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D110" s="1">
+        <f>VLOOKUP(C110,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E110" s="5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A111" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B111" s="1">
+        <v>109</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D111" s="1">
+        <f>VLOOKUP(C111,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E111" s="5">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A112" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B112" s="1">
+        <v>110</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D112" s="1">
+        <f>VLOOKUP(C112,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E112" s="5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A113" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B113" s="1">
+        <v>111</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D113" s="1">
+        <f>VLOOKUP(C113,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E113" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A114" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B114" s="1">
+        <v>112</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D114" s="1">
+        <f>VLOOKUP(C114,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E114" s="5">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A115" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B115" s="1">
+        <v>113</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D115" s="1">
+        <f>VLOOKUP(C115,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E115" s="5">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A116" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B116" s="1">
+        <v>114</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D116" s="1">
+        <f>VLOOKUP(C116,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E116" s="5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A117" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B117" s="1">
+        <v>115</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D117" s="1">
+        <f>VLOOKUP(C117,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E117" s="5">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A118" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B118" s="1">
+        <v>116</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D118" s="1">
+        <f>VLOOKUP(C118,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E118" s="5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A119" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B119" s="1">
+        <v>117</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D119" s="1">
+        <f>VLOOKUP(C119,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E119" s="5">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A120" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B120" s="1">
+        <v>118</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D120" s="1">
+        <f>VLOOKUP(C120,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E120" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A121" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B121" s="1">
+        <v>119</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D121" s="1">
+        <f>VLOOKUP(C121,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E121" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A122" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B122" s="1">
+        <v>120</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D122" s="1">
+        <f>VLOOKUP(C122,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E122" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A123" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B123" s="1">
+        <v>121</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D123" s="1">
+        <f>VLOOKUP(C123,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E123" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A124" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B124" s="1">
+        <v>122</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D124" s="1">
+        <f>VLOOKUP(C124,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E124" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A125" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B125" s="1">
+        <v>123</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D125" s="1">
+        <f>VLOOKUP(C125,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E125" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A126" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B126" s="1">
+        <v>124</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D126" s="1">
+        <f>VLOOKUP(C126,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E126" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A127" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B127" s="1">
+        <v>125</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D127" s="1">
+        <f>VLOOKUP(C127,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E127" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A128" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B128" s="1">
+        <v>126</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D128" s="1">
+        <f>VLOOKUP(C128,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E128" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A129" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B129" s="1">
+        <v>127</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D129" s="1">
+        <f>VLOOKUP(C129,Device!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E129" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" ht="18.75" customHeight="1">
+      <c r="E130" s="6"/>
+    </row>
+    <row r="131" spans="1:5" ht="18.75" customHeight="1">
+      <c r="E131" s="6"/>
+    </row>
+    <row r="132" spans="1:5" ht="18.75" customHeight="1">
+      <c r="E132" s="6"/>
+    </row>
+    <row r="133" spans="1:5" ht="18.75" customHeight="1">
+      <c r="E133" s="6"/>
+    </row>
+    <row r="134" spans="1:5" ht="18.75" customHeight="1">
+      <c r="E134" s="6"/>
+    </row>
+    <row r="135" spans="1:5" ht="18.75" customHeight="1">
+      <c r="E135" s="6"/>
+    </row>
+    <row r="136" spans="1:5" ht="18.75" customHeight="1">
+      <c r="E136" s="6"/>
+    </row>
+    <row r="137" spans="1:5" ht="18.75" customHeight="1">
+      <c r="E137" s="6"/>
+    </row>
+    <row r="138" spans="1:5" ht="18.75" customHeight="1">
+      <c r="E138" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -1142,7 +3377,7 @@
           <x14:formula1>
             <xm:f>Device!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C29</xm:sqref>
+          <xm:sqref>C2:C129</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1164,46 +3399,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -1211,33 +3446,33 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I2" s="2">
+        <v>33</v>
+      </c>
+      <c r="I2" s="2" t="e">
         <f>VLOOKUP(C2,KeyCode!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="J2" s="2">
+        <v>#N/A</v>
+      </c>
+      <c r="J2" s="2" t="e">
         <f>VLOOKUP(D2,KeyCode!A:B,2,FALSE)</f>
-        <v>17</v>
+        <v>#N/A</v>
       </c>
       <c r="K2" s="2">
         <f>VLOOKUP(E2,KeyCode!A:B,2,FALSE)</f>
@@ -1261,33 +3496,33 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I3" s="2">
+        <v>33</v>
+      </c>
+      <c r="I3" s="2" t="e">
         <f>VLOOKUP(C3,KeyCode!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="J3" s="2">
+        <v>#N/A</v>
+      </c>
+      <c r="J3" s="2" t="e">
         <f>VLOOKUP(D3,KeyCode!A:B,2,FALSE)</f>
-        <v>18</v>
+        <v>#N/A</v>
       </c>
       <c r="K3" s="2">
         <f>VLOOKUP(E3,KeyCode!A:B,2,FALSE)</f>
@@ -1311,33 +3546,33 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I4" s="2">
+        <v>33</v>
+      </c>
+      <c r="I4" s="2" t="e">
         <f>VLOOKUP(C4,KeyCode!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="J4" s="2">
+        <v>#N/A</v>
+      </c>
+      <c r="J4" s="2" t="e">
         <f>VLOOKUP(D4,KeyCode!A:B,2,FALSE)</f>
-        <v>19</v>
+        <v>#N/A</v>
       </c>
       <c r="K4" s="2">
         <f>VLOOKUP(E4,KeyCode!A:B,2,FALSE)</f>
@@ -1361,33 +3596,33 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I5" s="2">
+        <v>33</v>
+      </c>
+      <c r="I5" s="2" t="e">
         <f>VLOOKUP(C5,KeyCode!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="J5" s="2">
+        <v>#N/A</v>
+      </c>
+      <c r="J5" s="2" t="e">
         <f>VLOOKUP(D5,KeyCode!A:B,2,FALSE)</f>
-        <v>20</v>
+        <v>#N/A</v>
       </c>
       <c r="K5" s="2">
         <f>VLOOKUP(E5,KeyCode!A:B,2,FALSE)</f>
@@ -1411,29 +3646,29 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I6" s="2">
+        <v>33</v>
+      </c>
+      <c r="I6" s="2" t="e">
         <f>VLOOKUP(C6,KeyCode!A:B,2,FALSE)</f>
-        <v>6</v>
+        <v>#N/A</v>
       </c>
       <c r="J6" s="2">
         <f>VLOOKUP(D6,KeyCode!A:B,2,FALSE)</f>
@@ -1461,29 +3696,29 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I7" s="2">
+        <v>33</v>
+      </c>
+      <c r="I7" s="2" t="e">
         <f>VLOOKUP(C7,KeyCode!A:B,2,FALSE)</f>
-        <v>7</v>
+        <v>#N/A</v>
       </c>
       <c r="J7" s="2">
         <f>VLOOKUP(D7,KeyCode!A:B,2,FALSE)</f>
@@ -1511,29 +3746,29 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I8" s="2">
+        <v>33</v>
+      </c>
+      <c r="I8" s="2" t="e">
         <f>VLOOKUP(C8,KeyCode!A:B,2,FALSE)</f>
-        <v>5</v>
+        <v>#N/A</v>
       </c>
       <c r="J8" s="2">
         <f>VLOOKUP(D8,KeyCode!A:B,2,FALSE)</f>
@@ -1561,29 +3796,29 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I9" s="2">
+        <v>33</v>
+      </c>
+      <c r="I9" s="2" t="e">
         <f>VLOOKUP(C9,KeyCode!A:B,2,FALSE)</f>
-        <v>9</v>
+        <v>#N/A</v>
       </c>
       <c r="J9" s="2">
         <f>VLOOKUP(D9,KeyCode!A:B,2,FALSE)</f>
@@ -1611,29 +3846,29 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I10" s="2">
+        <v>33</v>
+      </c>
+      <c r="I10" s="2" t="e">
         <f>VLOOKUP(C10,KeyCode!A:B,2,FALSE)</f>
-        <v>26</v>
+        <v>#N/A</v>
       </c>
       <c r="J10" s="2">
         <f>VLOOKUP(D10,KeyCode!A:B,2,FALSE)</f>
@@ -1661,33 +3896,33 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I11" s="2">
+        <v>33</v>
+      </c>
+      <c r="I11" s="2" t="e">
         <f>VLOOKUP(C11,KeyCode!A:B,2,FALSE)</f>
-        <v>26</v>
-      </c>
-      <c r="J11" s="2">
+        <v>#N/A</v>
+      </c>
+      <c r="J11" s="2" t="e">
         <f>VLOOKUP(D11,KeyCode!A:B,2,FALSE)</f>
-        <v>25</v>
+        <v>#N/A</v>
       </c>
       <c r="K11" s="2">
         <f>VLOOKUP(E11,KeyCode!A:B,2,FALSE)</f>
@@ -1711,29 +3946,29 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I12" s="2">
+        <v>33</v>
+      </c>
+      <c r="I12" s="2" t="e">
         <f>VLOOKUP(C12,KeyCode!A:B,2,FALSE)</f>
-        <v>27</v>
+        <v>#N/A</v>
       </c>
       <c r="J12" s="2">
         <f>VLOOKUP(D12,KeyCode!A:B,2,FALSE)</f>
@@ -1761,29 +3996,29 @@
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I13" s="2">
+        <v>33</v>
+      </c>
+      <c r="I13" s="2" t="e">
         <f>VLOOKUP(C13,KeyCode!A:B,2,FALSE)</f>
-        <v>14</v>
+        <v>#N/A</v>
       </c>
       <c r="J13" s="2">
         <f>VLOOKUP(D13,KeyCode!A:B,2,FALSE)</f>
@@ -1811,29 +4046,29 @@
         <v>12</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I14" s="2">
+        <v>33</v>
+      </c>
+      <c r="I14" s="2" t="e">
         <f>VLOOKUP(C14,KeyCode!A:B,2,FALSE)</f>
-        <v>15</v>
+        <v>#N/A</v>
       </c>
       <c r="J14" s="2">
         <f>VLOOKUP(D14,KeyCode!A:B,2,FALSE)</f>
@@ -1861,29 +4096,29 @@
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I15" s="2">
+        <v>33</v>
+      </c>
+      <c r="I15" s="2" t="e">
         <f>VLOOKUP(C15,KeyCode!A:B,2,FALSE)</f>
-        <v>7</v>
+        <v>#N/A</v>
       </c>
       <c r="J15" s="2">
         <f>VLOOKUP(D15,KeyCode!A:B,2,FALSE)</f>
@@ -1911,29 +4146,29 @@
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I16" s="2">
+        <v>33</v>
+      </c>
+      <c r="I16" s="2" t="e">
         <f>VLOOKUP(C16,KeyCode!A:B,2,FALSE)</f>
-        <v>25</v>
+        <v>#N/A</v>
       </c>
       <c r="J16" s="2">
         <f>VLOOKUP(D16,KeyCode!A:B,2,FALSE)</f>
@@ -1961,7 +4196,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>1</v>
@@ -1970,24 +4205,24 @@
         <v>3</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I17" s="2">
+        <v>33</v>
+      </c>
+      <c r="I17" s="2" t="e">
         <f>VLOOKUP(C17,KeyCode!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="J17" s="2">
+        <v>#N/A</v>
+      </c>
+      <c r="J17" s="2" t="e">
         <f>VLOOKUP(D17,KeyCode!A:B,2,FALSE)</f>
-        <v>4</v>
+        <v>#N/A</v>
       </c>
       <c r="K17" s="2">
         <f>VLOOKUP(E17,KeyCode!A:B,2,FALSE)</f>
@@ -2011,29 +4246,29 @@
         <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I18" s="2">
+        <v>33</v>
+      </c>
+      <c r="I18" s="2" t="e">
         <f>VLOOKUP(C18,KeyCode!A:B,2,FALSE)</f>
-        <v>8</v>
+        <v>#N/A</v>
       </c>
       <c r="J18" s="2">
         <f>VLOOKUP(D18,KeyCode!A:B,2,FALSE)</f>
@@ -2061,29 +4296,29 @@
         <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I19" s="2">
+        <v>33</v>
+      </c>
+      <c r="I19" s="2" t="e">
         <f>VLOOKUP(C19,KeyCode!A:B,2,FALSE)</f>
-        <v>6</v>
+        <v>#N/A</v>
       </c>
       <c r="J19" s="2">
         <f>VLOOKUP(D19,KeyCode!A:B,2,FALSE)</f>
@@ -2132,7 +4367,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B1">
         <v>-1</v>
@@ -2140,7 +4375,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2148,7 +4383,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -2156,7 +4391,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B4">
         <v>2</v>

--- a/DXLibProject_Start/Data/CSV/KeyCode.xlsx
+++ b/DXLibProject_Start/Data/CSV/KeyCode.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9664323D-05B2-4F18-90CB-FA81F1E6126F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AE5B920-15FC-4F5F-AC84-7E2792B3AEC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4050" yWindow="-13485" windowWidth="21585" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15" yWindow="-11490" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KeyCode" sheetId="1" r:id="rId1"/>
@@ -41,51 +41,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="189">
   <si>
-    <t>GpUp</t>
-  </si>
-  <si>
-    <t>GpRight</t>
-  </si>
-  <si>
-    <t>GpDown</t>
-  </si>
-  <si>
-    <t>GpLeft</t>
-  </si>
-  <si>
-    <t>GpNorth</t>
-  </si>
-  <si>
-    <t>GpEast</t>
-  </si>
-  <si>
-    <t>GpSouth</t>
-  </si>
-  <si>
-    <t>GpWest</t>
-  </si>
-  <si>
-    <t>GpStart</t>
-  </si>
-  <si>
-    <t>GpRightTrigger</t>
-  </si>
-  <si>
-    <t>GpLeftThumb</t>
-  </si>
-  <si>
-    <t>GpLeftThumbUp</t>
-  </si>
-  <si>
-    <t>GpLeftThumbRight</t>
-  </si>
-  <si>
-    <t>GpLeftThumbDown</t>
-  </si>
-  <si>
-    <t>GpLeftThumbLeft</t>
-  </si>
-  <si>
     <t>GamePad</t>
   </si>
   <si>
@@ -208,9 +163,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>GpCross</t>
-  </si>
-  <si>
     <t>DragonCall</t>
   </si>
   <si>
@@ -225,12 +177,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>GpLeftVector</t>
-  </si>
-  <si>
-    <t>GpRightVector</t>
-  </si>
-  <si>
     <t>CursorMove</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -634,6 +580,60 @@
   </si>
   <si>
     <t>Gp_RightVector</t>
+  </si>
+  <si>
+    <t>Gp_Up</t>
+  </si>
+  <si>
+    <t>Gp_Down</t>
+  </si>
+  <si>
+    <t>GP_Left</t>
+  </si>
+  <si>
+    <t>GP_East</t>
+  </si>
+  <si>
+    <t>GP_South</t>
+  </si>
+  <si>
+    <t>GP_North</t>
+  </si>
+  <si>
+    <t>GP_Start</t>
+  </si>
+  <si>
+    <t>GP_LeftVector</t>
+  </si>
+  <si>
+    <t>GP_RightVector</t>
+  </si>
+  <si>
+    <t>GP_RightTrigger</t>
+  </si>
+  <si>
+    <t>GP_LeftThumb</t>
+  </si>
+  <si>
+    <t>GP_Cross</t>
+  </si>
+  <si>
+    <t>GP_Right</t>
+  </si>
+  <si>
+    <t>GP_West</t>
+  </si>
+  <si>
+    <t>GP_LeftThumbUp</t>
+  </si>
+  <si>
+    <t>GP_LeftThumbRight</t>
+  </si>
+  <si>
+    <t>GP_LeftThumbDown</t>
+  </si>
+  <si>
+    <t>GP_LeftThumbLeft</t>
   </si>
 </sst>
 </file>
@@ -684,7 +684,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -707,11 +707,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -727,6 +738,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1020,30 +1034,30 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18.75" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D2" s="1">
         <f>VLOOKUP(C2,Device!A:B,2,FALSE)</f>
@@ -1055,13 +1069,13 @@
     </row>
     <row r="3" spans="1:5" ht="18.75" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D3" s="1">
         <f>VLOOKUP(C3,Device!A:B,2,FALSE)</f>
@@ -1073,13 +1087,13 @@
     </row>
     <row r="4" spans="1:5" ht="18.75" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D4" s="1">
         <f>VLOOKUP(C4,Device!A:B,2,FALSE)</f>
@@ -1091,13 +1105,13 @@
     </row>
     <row r="5" spans="1:5" ht="18.75" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="B5" s="1">
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D5" s="1">
         <f>VLOOKUP(C5,Device!A:B,2,FALSE)</f>
@@ -1109,13 +1123,13 @@
     </row>
     <row r="6" spans="1:5" ht="18.75" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="B6" s="1">
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D6" s="1">
         <f>VLOOKUP(C6,Device!A:B,2,FALSE)</f>
@@ -1127,13 +1141,13 @@
     </row>
     <row r="7" spans="1:5" ht="18.75" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="B7" s="1">
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D7" s="1">
         <f>VLOOKUP(C7,Device!A:B,2,FALSE)</f>
@@ -1145,13 +1159,13 @@
     </row>
     <row r="8" spans="1:5" ht="18.75" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="B8" s="1">
         <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D8" s="1">
         <f>VLOOKUP(C8,Device!A:B,2,FALSE)</f>
@@ -1163,13 +1177,13 @@
     </row>
     <row r="9" spans="1:5" ht="18.75" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="B9" s="1">
         <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D9" s="1">
         <f>VLOOKUP(C9,Device!A:B,2,FALSE)</f>
@@ -1181,13 +1195,13 @@
     </row>
     <row r="10" spans="1:5" ht="18.75" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="B10" s="1">
         <v>8</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D10" s="1">
         <f>VLOOKUP(C10,Device!A:B,2,FALSE)</f>
@@ -1199,13 +1213,13 @@
     </row>
     <row r="11" spans="1:5" ht="18.75" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="B11" s="1">
         <v>9</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D11" s="1">
         <f>VLOOKUP(C11,Device!A:B,2,FALSE)</f>
@@ -1217,13 +1231,13 @@
     </row>
     <row r="12" spans="1:5" ht="18.75" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="B12" s="1">
         <v>10</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D12" s="1">
         <f>VLOOKUP(C12,Device!A:B,2,FALSE)</f>
@@ -1235,13 +1249,13 @@
     </row>
     <row r="13" spans="1:5" ht="18.75" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="B13" s="1">
         <v>11</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D13" s="1">
         <f>VLOOKUP(C13,Device!A:B,2,FALSE)</f>
@@ -1253,13 +1267,13 @@
     </row>
     <row r="14" spans="1:5" ht="18.75" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="B14" s="1">
         <v>12</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D14" s="1">
         <f>VLOOKUP(C14,Device!A:B,2,FALSE)</f>
@@ -1271,13 +1285,13 @@
     </row>
     <row r="15" spans="1:5" ht="18.75" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="B15" s="1">
         <v>13</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D15" s="1">
         <f>VLOOKUP(C15,Device!A:B,2,FALSE)</f>
@@ -1289,13 +1303,13 @@
     </row>
     <row r="16" spans="1:5" ht="18.75" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="B16" s="1">
         <v>14</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D16" s="1">
         <f>VLOOKUP(C16,Device!A:B,2,FALSE)</f>
@@ -1307,13 +1321,13 @@
     </row>
     <row r="17" spans="1:5" ht="18.75" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="B17" s="1">
         <v>15</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D17" s="1">
         <f>VLOOKUP(C17,Device!A:B,2,FALSE)</f>
@@ -1325,13 +1339,13 @@
     </row>
     <row r="18" spans="1:5" ht="18.75" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="B18" s="1">
         <v>16</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D18" s="1">
         <f>VLOOKUP(C18,Device!A:B,2,FALSE)</f>
@@ -1343,13 +1357,13 @@
     </row>
     <row r="19" spans="1:5" ht="18.75" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="B19" s="1">
         <v>17</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D19" s="1">
         <f>VLOOKUP(C19,Device!A:B,2,FALSE)</f>
@@ -1361,13 +1375,13 @@
     </row>
     <row r="20" spans="1:5" ht="18.75" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="B20" s="1">
         <v>18</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D20" s="1">
         <f>VLOOKUP(C20,Device!A:B,2,FALSE)</f>
@@ -1379,13 +1393,13 @@
     </row>
     <row r="21" spans="1:5" ht="18.75" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="B21" s="1">
         <v>19</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D21" s="1">
         <f>VLOOKUP(C21,Device!A:B,2,FALSE)</f>
@@ -1397,13 +1411,13 @@
     </row>
     <row r="22" spans="1:5" ht="18.75" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="B22" s="1">
         <v>20</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D22" s="1">
         <f>VLOOKUP(C22,Device!A:B,2,FALSE)</f>
@@ -1415,13 +1429,13 @@
     </row>
     <row r="23" spans="1:5" ht="18.75" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="B23" s="1">
         <v>21</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D23" s="1">
         <f>VLOOKUP(C23,Device!A:B,2,FALSE)</f>
@@ -1433,13 +1447,13 @@
     </row>
     <row r="24" spans="1:5" ht="18.75" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="B24" s="1">
         <v>22</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D24" s="1">
         <f>VLOOKUP(C24,Device!A:B,2,FALSE)</f>
@@ -1451,13 +1465,13 @@
     </row>
     <row r="25" spans="1:5" ht="18.75" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="B25" s="1">
         <v>23</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D25" s="1">
         <f>VLOOKUP(C25,Device!A:B,2,FALSE)</f>
@@ -1469,13 +1483,13 @@
     </row>
     <row r="26" spans="1:5" ht="18.75" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="B26" s="1">
         <v>24</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D26" s="1">
         <f>VLOOKUP(C26,Device!A:B,2,FALSE)</f>
@@ -1487,13 +1501,13 @@
     </row>
     <row r="27" spans="1:5" ht="18.75" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="B27" s="1">
         <v>25</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D27" s="1">
         <f>VLOOKUP(C27,Device!A:B,2,FALSE)</f>
@@ -1505,13 +1519,13 @@
     </row>
     <row r="28" spans="1:5" ht="18.75" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="B28" s="1">
         <v>26</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D28" s="1">
         <f>VLOOKUP(C28,Device!A:B,2,FALSE)</f>
@@ -1523,13 +1537,13 @@
     </row>
     <row r="29" spans="1:5" ht="18.75" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="B29" s="1">
         <v>27</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D29" s="1">
         <f>VLOOKUP(C29,Device!A:B,2,FALSE)</f>
@@ -1541,13 +1555,13 @@
     </row>
     <row r="30" spans="1:5" ht="18.75" customHeight="1">
       <c r="A30" s="4" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="B30" s="1">
         <v>28</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D30" s="1">
         <f>VLOOKUP(C30,Device!A:B,2,FALSE)</f>
@@ -1559,13 +1573,13 @@
     </row>
     <row r="31" spans="1:5" ht="18.75" customHeight="1">
       <c r="A31" s="4" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="B31" s="1">
         <v>29</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D31" s="1">
         <f>VLOOKUP(C31,Device!A:B,2,FALSE)</f>
@@ -1577,13 +1591,13 @@
     </row>
     <row r="32" spans="1:5" ht="18.75" customHeight="1">
       <c r="A32" s="4" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="B32" s="1">
         <v>30</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D32" s="1">
         <f>VLOOKUP(C32,Device!A:B,2,FALSE)</f>
@@ -1595,13 +1609,13 @@
     </row>
     <row r="33" spans="1:5" ht="18.75" customHeight="1">
       <c r="A33" s="4" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="B33" s="1">
         <v>31</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D33" s="1">
         <f>VLOOKUP(C33,Device!A:B,2,FALSE)</f>
@@ -1613,13 +1627,13 @@
     </row>
     <row r="34" spans="1:5" ht="18.75" customHeight="1">
       <c r="A34" s="4" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="B34" s="1">
         <v>32</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D34" s="1">
         <f>VLOOKUP(C34,Device!A:B,2,FALSE)</f>
@@ -1631,13 +1645,13 @@
     </row>
     <row r="35" spans="1:5" ht="18.75" customHeight="1">
       <c r="A35" s="4" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="B35" s="1">
         <v>33</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D35" s="1">
         <f>VLOOKUP(C35,Device!A:B,2,FALSE)</f>
@@ -1649,13 +1663,13 @@
     </row>
     <row r="36" spans="1:5" ht="18.75" customHeight="1">
       <c r="A36" s="4" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="B36" s="1">
         <v>34</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D36" s="1">
         <f>VLOOKUP(C36,Device!A:B,2,FALSE)</f>
@@ -1667,13 +1681,13 @@
     </row>
     <row r="37" spans="1:5" ht="18.75" customHeight="1">
       <c r="A37" s="4" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="B37" s="1">
         <v>35</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D37" s="1">
         <f>VLOOKUP(C37,Device!A:B,2,FALSE)</f>
@@ -1685,13 +1699,13 @@
     </row>
     <row r="38" spans="1:5" ht="18.75" customHeight="1">
       <c r="A38" s="4" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="B38" s="1">
         <v>36</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D38" s="1">
         <f>VLOOKUP(C38,Device!A:B,2,FALSE)</f>
@@ -1703,13 +1717,13 @@
     </row>
     <row r="39" spans="1:5" ht="18.75" customHeight="1">
       <c r="A39" s="4" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="B39" s="1">
         <v>37</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D39" s="1">
         <f>VLOOKUP(C39,Device!A:B,2,FALSE)</f>
@@ -1721,13 +1735,13 @@
     </row>
     <row r="40" spans="1:5" ht="18.75" customHeight="1">
       <c r="A40" s="4" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="B40" s="1">
         <v>38</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D40" s="1">
         <f>VLOOKUP(C40,Device!A:B,2,FALSE)</f>
@@ -1739,13 +1753,13 @@
     </row>
     <row r="41" spans="1:5" ht="18.75" customHeight="1">
       <c r="A41" s="4" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="B41" s="1">
         <v>39</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D41" s="1">
         <f>VLOOKUP(C41,Device!A:B,2,FALSE)</f>
@@ -1757,13 +1771,13 @@
     </row>
     <row r="42" spans="1:5" ht="18.75" customHeight="1">
       <c r="A42" s="4" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="B42" s="1">
         <v>40</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D42" s="1">
         <f>VLOOKUP(C42,Device!A:B,2,FALSE)</f>
@@ -1775,13 +1789,13 @@
     </row>
     <row r="43" spans="1:5" ht="18.75" customHeight="1">
       <c r="A43" s="4" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="B43" s="1">
         <v>41</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D43" s="1">
         <f>VLOOKUP(C43,Device!A:B,2,FALSE)</f>
@@ -1793,13 +1807,13 @@
     </row>
     <row r="44" spans="1:5" ht="18.75" customHeight="1">
       <c r="A44" s="4" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="B44" s="1">
         <v>42</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D44" s="1">
         <f>VLOOKUP(C44,Device!A:B,2,FALSE)</f>
@@ -1811,13 +1825,13 @@
     </row>
     <row r="45" spans="1:5" ht="18.75" customHeight="1">
       <c r="A45" s="4" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="B45" s="1">
         <v>43</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D45" s="1">
         <f>VLOOKUP(C45,Device!A:B,2,FALSE)</f>
@@ -1829,13 +1843,13 @@
     </row>
     <row r="46" spans="1:5" ht="18.75" customHeight="1">
       <c r="A46" s="4" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="B46" s="1">
         <v>44</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D46" s="1">
         <f>VLOOKUP(C46,Device!A:B,2,FALSE)</f>
@@ -1847,13 +1861,13 @@
     </row>
     <row r="47" spans="1:5" ht="18.75" customHeight="1">
       <c r="A47" s="4" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="B47" s="1">
         <v>45</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D47" s="1">
         <f>VLOOKUP(C47,Device!A:B,2,FALSE)</f>
@@ -1865,13 +1879,13 @@
     </row>
     <row r="48" spans="1:5" ht="18.75" customHeight="1">
       <c r="A48" s="4" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="B48" s="1">
         <v>46</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D48" s="1">
         <f>VLOOKUP(C48,Device!A:B,2,FALSE)</f>
@@ -1883,13 +1897,13 @@
     </row>
     <row r="49" spans="1:5" ht="18.75" customHeight="1">
       <c r="A49" s="4" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="B49" s="1">
         <v>47</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D49" s="1">
         <f>VLOOKUP(C49,Device!A:B,2,FALSE)</f>
@@ -1901,13 +1915,13 @@
     </row>
     <row r="50" spans="1:5" ht="18.75" customHeight="1">
       <c r="A50" s="4" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="B50" s="1">
         <v>48</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D50" s="1">
         <f>VLOOKUP(C50,Device!A:B,2,FALSE)</f>
@@ -1919,13 +1933,13 @@
     </row>
     <row r="51" spans="1:5" ht="18.75" customHeight="1">
       <c r="A51" s="4" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="B51" s="1">
         <v>49</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D51" s="1">
         <f>VLOOKUP(C51,Device!A:B,2,FALSE)</f>
@@ -1937,13 +1951,13 @@
     </row>
     <row r="52" spans="1:5" ht="18.75" customHeight="1">
       <c r="A52" s="4" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="B52" s="1">
         <v>50</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D52" s="1">
         <f>VLOOKUP(C52,Device!A:B,2,FALSE)</f>
@@ -1955,13 +1969,13 @@
     </row>
     <row r="53" spans="1:5" ht="18.75" customHeight="1">
       <c r="A53" s="4" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="B53" s="1">
         <v>51</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D53" s="1">
         <f>VLOOKUP(C53,Device!A:B,2,FALSE)</f>
@@ -1973,13 +1987,13 @@
     </row>
     <row r="54" spans="1:5" ht="18.75" customHeight="1">
       <c r="A54" s="4" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="B54" s="1">
         <v>52</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D54" s="1">
         <f>VLOOKUP(C54,Device!A:B,2,FALSE)</f>
@@ -1991,13 +2005,13 @@
     </row>
     <row r="55" spans="1:5" ht="18.75" customHeight="1">
       <c r="A55" s="4" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="B55" s="1">
         <v>53</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D55" s="1">
         <f>VLOOKUP(C55,Device!A:B,2,FALSE)</f>
@@ -2009,13 +2023,13 @@
     </row>
     <row r="56" spans="1:5" ht="18.75" customHeight="1">
       <c r="A56" s="4" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="B56" s="1">
         <v>54</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D56" s="1">
         <f>VLOOKUP(C56,Device!A:B,2,FALSE)</f>
@@ -2027,13 +2041,13 @@
     </row>
     <row r="57" spans="1:5" ht="18.75" customHeight="1">
       <c r="A57" s="4" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="B57" s="1">
         <v>55</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D57" s="1">
         <f>VLOOKUP(C57,Device!A:B,2,FALSE)</f>
@@ -2045,13 +2059,13 @@
     </row>
     <row r="58" spans="1:5" ht="18.75" customHeight="1">
       <c r="A58" s="4" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="B58" s="1">
         <v>56</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D58" s="1">
         <f>VLOOKUP(C58,Device!A:B,2,FALSE)</f>
@@ -2063,13 +2077,13 @@
     </row>
     <row r="59" spans="1:5" ht="18.75" customHeight="1">
       <c r="A59" s="4" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="B59" s="1">
         <v>57</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D59" s="1">
         <f>VLOOKUP(C59,Device!A:B,2,FALSE)</f>
@@ -2081,13 +2095,13 @@
     </row>
     <row r="60" spans="1:5" ht="18.75" customHeight="1">
       <c r="A60" s="4" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="B60" s="1">
         <v>58</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D60" s="1">
         <f>VLOOKUP(C60,Device!A:B,2,FALSE)</f>
@@ -2099,13 +2113,13 @@
     </row>
     <row r="61" spans="1:5" ht="18.75" customHeight="1">
       <c r="A61" s="4" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="B61" s="1">
         <v>59</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D61" s="1">
         <f>VLOOKUP(C61,Device!A:B,2,FALSE)</f>
@@ -2117,13 +2131,13 @@
     </row>
     <row r="62" spans="1:5" ht="18.75" customHeight="1">
       <c r="A62" s="4" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="B62" s="1">
         <v>60</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D62" s="1">
         <f>VLOOKUP(C62,Device!A:B,2,FALSE)</f>
@@ -2135,13 +2149,13 @@
     </row>
     <row r="63" spans="1:5" ht="18.75" customHeight="1">
       <c r="A63" s="4" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="B63" s="1">
         <v>61</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D63" s="1">
         <f>VLOOKUP(C63,Device!A:B,2,FALSE)</f>
@@ -2153,13 +2167,13 @@
     </row>
     <row r="64" spans="1:5" ht="18.75" customHeight="1">
       <c r="A64" s="4" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B64" s="1">
         <v>62</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D64" s="1">
         <f>VLOOKUP(C64,Device!A:B,2,FALSE)</f>
@@ -2171,13 +2185,13 @@
     </row>
     <row r="65" spans="1:5" ht="18.75" customHeight="1">
       <c r="A65" s="4" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="B65" s="1">
         <v>63</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D65" s="1">
         <f>VLOOKUP(C65,Device!A:B,2,FALSE)</f>
@@ -2189,13 +2203,13 @@
     </row>
     <row r="66" spans="1:5" ht="18.75" customHeight="1">
       <c r="A66" s="4" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="B66" s="1">
         <v>64</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D66" s="1">
         <f>VLOOKUP(C66,Device!A:B,2,FALSE)</f>
@@ -2207,13 +2221,13 @@
     </row>
     <row r="67" spans="1:5" ht="18.75" customHeight="1">
       <c r="A67" s="4" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="B67" s="1">
         <v>65</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D67" s="1">
         <f>VLOOKUP(C67,Device!A:B,2,FALSE)</f>
@@ -2225,13 +2239,13 @@
     </row>
     <row r="68" spans="1:5" ht="18.75" customHeight="1">
       <c r="A68" s="4" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="B68" s="1">
         <v>66</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D68" s="1">
         <f>VLOOKUP(C68,Device!A:B,2,FALSE)</f>
@@ -2243,13 +2257,13 @@
     </row>
     <row r="69" spans="1:5" ht="18.75" customHeight="1">
       <c r="A69" s="4" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="B69" s="1">
         <v>67</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D69" s="1">
         <f>VLOOKUP(C69,Device!A:B,2,FALSE)</f>
@@ -2261,13 +2275,13 @@
     </row>
     <row r="70" spans="1:5" ht="18.75" customHeight="1">
       <c r="A70" s="4" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="B70" s="1">
         <v>68</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D70" s="1">
         <f>VLOOKUP(C70,Device!A:B,2,FALSE)</f>
@@ -2279,13 +2293,13 @@
     </row>
     <row r="71" spans="1:5" ht="18.75" customHeight="1">
       <c r="A71" s="4" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="B71" s="1">
         <v>69</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D71" s="1">
         <f>VLOOKUP(C71,Device!A:B,2,FALSE)</f>
@@ -2297,13 +2311,13 @@
     </row>
     <row r="72" spans="1:5" ht="18.75" customHeight="1">
       <c r="A72" s="4" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="B72" s="1">
         <v>70</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D72" s="1">
         <f>VLOOKUP(C72,Device!A:B,2,FALSE)</f>
@@ -2315,13 +2329,13 @@
     </row>
     <row r="73" spans="1:5" ht="18.75" customHeight="1">
       <c r="A73" s="4" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="B73" s="1">
         <v>71</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D73" s="1">
         <f>VLOOKUP(C73,Device!A:B,2,FALSE)</f>
@@ -2333,13 +2347,13 @@
     </row>
     <row r="74" spans="1:5" ht="18.75" customHeight="1">
       <c r="A74" s="4" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="B74" s="1">
         <v>72</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D74" s="1">
         <f>VLOOKUP(C74,Device!A:B,2,FALSE)</f>
@@ -2351,13 +2365,13 @@
     </row>
     <row r="75" spans="1:5" ht="18.75" customHeight="1">
       <c r="A75" s="4" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="B75" s="1">
         <v>73</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D75" s="1">
         <f>VLOOKUP(C75,Device!A:B,2,FALSE)</f>
@@ -2369,13 +2383,13 @@
     </row>
     <row r="76" spans="1:5" ht="18.75" customHeight="1">
       <c r="A76" s="4" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="B76" s="1">
         <v>74</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D76" s="1">
         <f>VLOOKUP(C76,Device!A:B,2,FALSE)</f>
@@ -2387,13 +2401,13 @@
     </row>
     <row r="77" spans="1:5" ht="18.75" customHeight="1">
       <c r="A77" s="4" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="B77" s="1">
         <v>75</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D77" s="1">
         <f>VLOOKUP(C77,Device!A:B,2,FALSE)</f>
@@ -2405,13 +2419,13 @@
     </row>
     <row r="78" spans="1:5" ht="18.75" customHeight="1">
       <c r="A78" s="4" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="B78" s="1">
         <v>76</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D78" s="1">
         <f>VLOOKUP(C78,Device!A:B,2,FALSE)</f>
@@ -2423,13 +2437,13 @@
     </row>
     <row r="79" spans="1:5" ht="18.75" customHeight="1">
       <c r="A79" s="4" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="B79" s="1">
         <v>77</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D79" s="1">
         <f>VLOOKUP(C79,Device!A:B,2,FALSE)</f>
@@ -2441,13 +2455,13 @@
     </row>
     <row r="80" spans="1:5" ht="18.75" customHeight="1">
       <c r="A80" s="4" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="B80" s="1">
         <v>78</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D80" s="1">
         <f>VLOOKUP(C80,Device!A:B,2,FALSE)</f>
@@ -2459,13 +2473,13 @@
     </row>
     <row r="81" spans="1:5" ht="18.75" customHeight="1">
       <c r="A81" s="4" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="B81" s="1">
         <v>79</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D81" s="1">
         <f>VLOOKUP(C81,Device!A:B,2,FALSE)</f>
@@ -2477,13 +2491,13 @@
     </row>
     <row r="82" spans="1:5" ht="18.75" customHeight="1">
       <c r="A82" s="4" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="B82" s="1">
         <v>80</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D82" s="1">
         <f>VLOOKUP(C82,Device!A:B,2,FALSE)</f>
@@ -2495,13 +2509,13 @@
     </row>
     <row r="83" spans="1:5" ht="18.75" customHeight="1">
       <c r="A83" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="B83" s="1">
         <v>81</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D83" s="1">
         <f>VLOOKUP(C83,Device!A:B,2,FALSE)</f>
@@ -2513,13 +2527,13 @@
     </row>
     <row r="84" spans="1:5" ht="18.75" customHeight="1">
       <c r="A84" s="4" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="B84" s="1">
         <v>82</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D84" s="1">
         <f>VLOOKUP(C84,Device!A:B,2,FALSE)</f>
@@ -2531,13 +2545,13 @@
     </row>
     <row r="85" spans="1:5" ht="18.75" customHeight="1">
       <c r="A85" s="4" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="B85" s="1">
         <v>83</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D85" s="1">
         <f>VLOOKUP(C85,Device!A:B,2,FALSE)</f>
@@ -2549,13 +2563,13 @@
     </row>
     <row r="86" spans="1:5" ht="18.75" customHeight="1">
       <c r="A86" s="4" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="B86" s="1">
         <v>84</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D86" s="1">
         <f>VLOOKUP(C86,Device!A:B,2,FALSE)</f>
@@ -2567,13 +2581,13 @@
     </row>
     <row r="87" spans="1:5" ht="18.75" customHeight="1">
       <c r="A87" s="4" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="B87" s="1">
         <v>85</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D87" s="1">
         <f>VLOOKUP(C87,Device!A:B,2,FALSE)</f>
@@ -2585,13 +2599,13 @@
     </row>
     <row r="88" spans="1:5" ht="18.75" customHeight="1">
       <c r="A88" s="4" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="B88" s="1">
         <v>86</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D88" s="1">
         <f>VLOOKUP(C88,Device!A:B,2,FALSE)</f>
@@ -2603,13 +2617,13 @@
     </row>
     <row r="89" spans="1:5" ht="18.75" customHeight="1">
       <c r="A89" s="4" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="B89" s="1">
         <v>87</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D89" s="1">
         <f>VLOOKUP(C89,Device!A:B,2,FALSE)</f>
@@ -2621,13 +2635,13 @@
     </row>
     <row r="90" spans="1:5" ht="18.75" customHeight="1">
       <c r="A90" s="4" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="B90" s="1">
         <v>88</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D90" s="1">
         <f>VLOOKUP(C90,Device!A:B,2,FALSE)</f>
@@ -2639,13 +2653,13 @@
     </row>
     <row r="91" spans="1:5" ht="18.75" customHeight="1">
       <c r="A91" s="4" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="B91" s="1">
         <v>89</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D91" s="1">
         <f>VLOOKUP(C91,Device!A:B,2,FALSE)</f>
@@ -2657,13 +2671,13 @@
     </row>
     <row r="92" spans="1:5" ht="18.75" customHeight="1">
       <c r="A92" s="4" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="B92" s="1">
         <v>90</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D92" s="1">
         <f>VLOOKUP(C92,Device!A:B,2,FALSE)</f>
@@ -2675,13 +2689,13 @@
     </row>
     <row r="93" spans="1:5" ht="18.75" customHeight="1">
       <c r="A93" s="4" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B93" s="1">
         <v>91</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D93" s="1">
         <f>VLOOKUP(C93,Device!A:B,2,FALSE)</f>
@@ -2693,13 +2707,13 @@
     </row>
     <row r="94" spans="1:5" ht="18.75" customHeight="1">
       <c r="A94" s="4" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="B94" s="1">
         <v>92</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D94" s="1">
         <f>VLOOKUP(C94,Device!A:B,2,FALSE)</f>
@@ -2711,13 +2725,13 @@
     </row>
     <row r="95" spans="1:5" ht="18.75" customHeight="1">
       <c r="A95" s="4" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B95" s="1">
         <v>93</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D95" s="1">
         <f>VLOOKUP(C95,Device!A:B,2,FALSE)</f>
@@ -2729,13 +2743,13 @@
     </row>
     <row r="96" spans="1:5" ht="18.75" customHeight="1">
       <c r="A96" s="4" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B96" s="1">
         <v>94</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D96" s="1">
         <f>VLOOKUP(C96,Device!A:B,2,FALSE)</f>
@@ -2747,13 +2761,13 @@
     </row>
     <row r="97" spans="1:5" ht="18.75" customHeight="1">
       <c r="A97" s="4" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="B97" s="1">
         <v>95</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D97" s="1">
         <f>VLOOKUP(C97,Device!A:B,2,FALSE)</f>
@@ -2765,13 +2779,13 @@
     </row>
     <row r="98" spans="1:5" ht="18.75" customHeight="1">
       <c r="A98" s="4" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B98" s="1">
         <v>96</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D98" s="1">
         <f>VLOOKUP(C98,Device!A:B,2,FALSE)</f>
@@ -2783,13 +2797,13 @@
     </row>
     <row r="99" spans="1:5" ht="18.75" customHeight="1">
       <c r="A99" s="4" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B99" s="1">
         <v>97</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D99" s="1">
         <f>VLOOKUP(C99,Device!A:B,2,FALSE)</f>
@@ -2801,13 +2815,13 @@
     </row>
     <row r="100" spans="1:5" ht="18.75" customHeight="1">
       <c r="A100" s="4" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="B100" s="1">
         <v>98</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D100" s="1">
         <f>VLOOKUP(C100,Device!A:B,2,FALSE)</f>
@@ -2819,13 +2833,13 @@
     </row>
     <row r="101" spans="1:5" ht="18.75" customHeight="1">
       <c r="A101" s="4" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="B101" s="1">
         <v>99</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D101" s="1">
         <f>VLOOKUP(C101,Device!A:B,2,FALSE)</f>
@@ -2837,13 +2851,13 @@
     </row>
     <row r="102" spans="1:5" ht="18.75" customHeight="1">
       <c r="A102" s="4" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="B102" s="1">
         <v>100</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D102" s="1">
         <f>VLOOKUP(C102,Device!A:B,2,FALSE)</f>
@@ -2855,13 +2869,13 @@
     </row>
     <row r="103" spans="1:5" ht="18.75" customHeight="1">
       <c r="A103" s="4" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="B103" s="1">
         <v>101</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D103" s="1">
         <f>VLOOKUP(C103,Device!A:B,2,FALSE)</f>
@@ -2873,13 +2887,13 @@
     </row>
     <row r="104" spans="1:5" ht="18.75" customHeight="1">
       <c r="A104" s="4" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B104" s="1">
         <v>102</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D104" s="1">
         <f>VLOOKUP(C104,Device!A:B,2,FALSE)</f>
@@ -2891,13 +2905,13 @@
     </row>
     <row r="105" spans="1:5" ht="18.75" customHeight="1">
       <c r="A105" s="4" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B105" s="1">
         <v>103</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D105" s="1">
         <f>VLOOKUP(C105,Device!A:B,2,FALSE)</f>
@@ -2909,13 +2923,13 @@
     </row>
     <row r="106" spans="1:5" ht="18.75" customHeight="1">
       <c r="A106" s="4" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B106" s="1">
         <v>104</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D106" s="1">
         <f>VLOOKUP(C106,Device!A:B,2,FALSE)</f>
@@ -2927,13 +2941,13 @@
     </row>
     <row r="107" spans="1:5" ht="18.75" customHeight="1">
       <c r="A107" s="4" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B107" s="1">
         <v>105</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D107" s="1">
         <f>VLOOKUP(C107,Device!A:B,2,FALSE)</f>
@@ -2945,13 +2959,13 @@
     </row>
     <row r="108" spans="1:5" ht="18.75" customHeight="1">
       <c r="A108" s="4" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="B108" s="1">
         <v>106</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D108" s="1">
         <f>VLOOKUP(C108,Device!A:B,2,FALSE)</f>
@@ -2963,13 +2977,13 @@
     </row>
     <row r="109" spans="1:5" ht="18.75" customHeight="1">
       <c r="A109" s="4" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B109" s="1">
         <v>107</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D109" s="1">
         <f>VLOOKUP(C109,Device!A:B,2,FALSE)</f>
@@ -2981,13 +2995,13 @@
     </row>
     <row r="110" spans="1:5" ht="18.75" customHeight="1">
       <c r="A110" s="4" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B110" s="1">
         <v>108</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D110" s="1">
         <f>VLOOKUP(C110,Device!A:B,2,FALSE)</f>
@@ -2999,13 +3013,13 @@
     </row>
     <row r="111" spans="1:5" ht="18.75" customHeight="1">
       <c r="A111" s="4" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B111" s="1">
         <v>109</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D111" s="1">
         <f>VLOOKUP(C111,Device!A:B,2,FALSE)</f>
@@ -3017,13 +3031,13 @@
     </row>
     <row r="112" spans="1:5" ht="18.75" customHeight="1">
       <c r="A112" s="4" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="B112" s="1">
         <v>110</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D112" s="1">
         <f>VLOOKUP(C112,Device!A:B,2,FALSE)</f>
@@ -3035,13 +3049,13 @@
     </row>
     <row r="113" spans="1:5" ht="18.75" customHeight="1">
       <c r="A113" s="4" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B113" s="1">
         <v>111</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D113" s="1">
         <f>VLOOKUP(C113,Device!A:B,2,FALSE)</f>
@@ -3053,13 +3067,13 @@
     </row>
     <row r="114" spans="1:5" ht="18.75" customHeight="1">
       <c r="A114" s="4" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="B114" s="1">
         <v>112</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D114" s="1">
         <f>VLOOKUP(C114,Device!A:B,2,FALSE)</f>
@@ -3071,13 +3085,13 @@
     </row>
     <row r="115" spans="1:5" ht="18.75" customHeight="1">
       <c r="A115" s="4" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="B115" s="1">
         <v>113</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D115" s="1">
         <f>VLOOKUP(C115,Device!A:B,2,FALSE)</f>
@@ -3089,13 +3103,13 @@
     </row>
     <row r="116" spans="1:5" ht="18.75" customHeight="1">
       <c r="A116" s="4" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="B116" s="1">
         <v>114</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D116" s="1">
         <f>VLOOKUP(C116,Device!A:B,2,FALSE)</f>
@@ -3107,13 +3121,13 @@
     </row>
     <row r="117" spans="1:5" ht="18.75" customHeight="1">
       <c r="A117" s="4" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="B117" s="1">
         <v>115</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D117" s="1">
         <f>VLOOKUP(C117,Device!A:B,2,FALSE)</f>
@@ -3125,13 +3139,13 @@
     </row>
     <row r="118" spans="1:5" ht="18.75" customHeight="1">
       <c r="A118" s="4" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B118" s="1">
         <v>116</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D118" s="1">
         <f>VLOOKUP(C118,Device!A:B,2,FALSE)</f>
@@ -3143,13 +3157,13 @@
     </row>
     <row r="119" spans="1:5" ht="18.75" customHeight="1">
       <c r="A119" s="4" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B119" s="1">
         <v>117</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D119" s="1">
         <f>VLOOKUP(C119,Device!A:B,2,FALSE)</f>
@@ -3161,13 +3175,13 @@
     </row>
     <row r="120" spans="1:5" ht="18.75" customHeight="1">
       <c r="A120" s="4" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="B120" s="1">
         <v>118</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D120" s="1">
         <f>VLOOKUP(C120,Device!A:B,2,FALSE)</f>
@@ -3179,13 +3193,13 @@
     </row>
     <row r="121" spans="1:5" ht="18.75" customHeight="1">
       <c r="A121" s="4" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="B121" s="1">
         <v>119</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D121" s="1">
         <f>VLOOKUP(C121,Device!A:B,2,FALSE)</f>
@@ -3197,13 +3211,13 @@
     </row>
     <row r="122" spans="1:5" ht="18.75" customHeight="1">
       <c r="A122" s="4" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="B122" s="1">
         <v>120</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D122" s="1">
         <f>VLOOKUP(C122,Device!A:B,2,FALSE)</f>
@@ -3215,13 +3229,13 @@
     </row>
     <row r="123" spans="1:5" ht="18.75" customHeight="1">
       <c r="A123" s="4" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="B123" s="1">
         <v>121</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D123" s="1">
         <f>VLOOKUP(C123,Device!A:B,2,FALSE)</f>
@@ -3233,13 +3247,13 @@
     </row>
     <row r="124" spans="1:5" ht="18.75" customHeight="1">
       <c r="A124" s="4" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B124" s="1">
         <v>122</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D124" s="1">
         <f>VLOOKUP(C124,Device!A:B,2,FALSE)</f>
@@ -3251,13 +3265,13 @@
     </row>
     <row r="125" spans="1:5" ht="18.75" customHeight="1">
       <c r="A125" s="4" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B125" s="1">
         <v>123</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D125" s="1">
         <f>VLOOKUP(C125,Device!A:B,2,FALSE)</f>
@@ -3269,13 +3283,13 @@
     </row>
     <row r="126" spans="1:5" ht="18.75" customHeight="1">
       <c r="A126" s="4" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B126" s="1">
         <v>124</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D126" s="1">
         <f>VLOOKUP(C126,Device!A:B,2,FALSE)</f>
@@ -3287,13 +3301,13 @@
     </row>
     <row r="127" spans="1:5" ht="18.75" customHeight="1">
       <c r="A127" s="4" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B127" s="1">
         <v>125</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D127" s="1">
         <f>VLOOKUP(C127,Device!A:B,2,FALSE)</f>
@@ -3305,13 +3319,13 @@
     </row>
     <row r="128" spans="1:5" ht="18.75" customHeight="1">
       <c r="A128" s="4" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="B128" s="1">
         <v>126</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D128" s="1">
         <f>VLOOKUP(C128,Device!A:B,2,FALSE)</f>
@@ -3323,13 +3337,13 @@
     </row>
     <row r="129" spans="1:5" ht="18.75" customHeight="1">
       <c r="A129" s="4" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="B129" s="1">
         <v>127</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D129" s="1">
         <f>VLOOKUP(C129,Device!A:B,2,FALSE)</f>
@@ -3387,7 +3401,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C62AA4DB-6C78-44DC-A30A-4C66BF09A693}">
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="16.125" bestFit="1" customWidth="1"/>
@@ -3399,46 +3413,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -3446,33 +3460,33 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>11</v>
+        <v>185</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I2" s="2" t="e">
+        <v>18</v>
+      </c>
+      <c r="I2" s="2">
         <f>VLOOKUP(C2,KeyCode!A:B,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J2" s="2" t="e">
+        <v>1</v>
+      </c>
+      <c r="J2" s="2">
         <f>VLOOKUP(D2,KeyCode!A:B,2,FALSE)</f>
-        <v>#N/A</v>
+        <v>17</v>
       </c>
       <c r="K2" s="2">
         <f>VLOOKUP(E2,KeyCode!A:B,2,FALSE)</f>
@@ -3496,33 +3510,33 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1</v>
+        <v>145</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>12</v>
+        <v>186</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I3" s="2" t="e">
+        <v>18</v>
+      </c>
+      <c r="I3" s="2">
         <f>VLOOKUP(C3,KeyCode!A:B,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J3" s="2" t="e">
+        <v>2</v>
+      </c>
+      <c r="J3" s="2">
         <f>VLOOKUP(D3,KeyCode!A:B,2,FALSE)</f>
-        <v>#N/A</v>
+        <v>18</v>
       </c>
       <c r="K3" s="2">
         <f>VLOOKUP(E3,KeyCode!A:B,2,FALSE)</f>
@@ -3546,33 +3560,33 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>2</v>
+        <v>172</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>13</v>
+        <v>187</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I4" s="2" t="e">
+        <v>18</v>
+      </c>
+      <c r="I4" s="2">
         <f>VLOOKUP(C4,KeyCode!A:B,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J4" s="2" t="e">
+        <v>3</v>
+      </c>
+      <c r="J4" s="2">
         <f>VLOOKUP(D4,KeyCode!A:B,2,FALSE)</f>
-        <v>#N/A</v>
+        <v>19</v>
       </c>
       <c r="K4" s="2">
         <f>VLOOKUP(E4,KeyCode!A:B,2,FALSE)</f>
@@ -3596,33 +3610,33 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>3</v>
+        <v>173</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>14</v>
+        <v>188</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I5" s="2" t="e">
+        <v>18</v>
+      </c>
+      <c r="I5" s="2">
         <f>VLOOKUP(C5,KeyCode!A:B,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J5" s="2" t="e">
+        <v>4</v>
+      </c>
+      <c r="J5" s="2">
         <f>VLOOKUP(D5,KeyCode!A:B,2,FALSE)</f>
-        <v>#N/A</v>
+        <v>20</v>
       </c>
       <c r="K5" s="2">
         <f>VLOOKUP(E5,KeyCode!A:B,2,FALSE)</f>
@@ -3646,29 +3660,29 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>5</v>
+        <v>174</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I6" s="2" t="e">
+        <v>18</v>
+      </c>
+      <c r="I6" s="2">
         <f>VLOOKUP(C6,KeyCode!A:B,2,FALSE)</f>
-        <v>#N/A</v>
+        <v>6</v>
       </c>
       <c r="J6" s="2">
         <f>VLOOKUP(D6,KeyCode!A:B,2,FALSE)</f>
@@ -3696,29 +3710,29 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>6</v>
+        <v>175</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I7" s="2" t="e">
+        <v>18</v>
+      </c>
+      <c r="I7" s="2">
         <f>VLOOKUP(C7,KeyCode!A:B,2,FALSE)</f>
-        <v>#N/A</v>
+        <v>7</v>
       </c>
       <c r="J7" s="2">
         <f>VLOOKUP(D7,KeyCode!A:B,2,FALSE)</f>
@@ -3746,29 +3760,29 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>4</v>
+        <v>176</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I8" s="2" t="e">
+        <v>18</v>
+      </c>
+      <c r="I8" s="2">
         <f>VLOOKUP(C8,KeyCode!A:B,2,FALSE)</f>
-        <v>#N/A</v>
+        <v>5</v>
       </c>
       <c r="J8" s="2">
         <f>VLOOKUP(D8,KeyCode!A:B,2,FALSE)</f>
@@ -3796,29 +3810,29 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>8</v>
+        <v>177</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I9" s="2" t="e">
+        <v>18</v>
+      </c>
+      <c r="I9" s="2">
         <f>VLOOKUP(C9,KeyCode!A:B,2,FALSE)</f>
-        <v>#N/A</v>
+        <v>9</v>
       </c>
       <c r="J9" s="2">
         <f>VLOOKUP(D9,KeyCode!A:B,2,FALSE)</f>
@@ -3846,29 +3860,29 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>55</v>
+        <v>178</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I10" s="2" t="e">
+        <v>18</v>
+      </c>
+      <c r="I10" s="2">
         <f>VLOOKUP(C10,KeyCode!A:B,2,FALSE)</f>
-        <v>#N/A</v>
+        <v>26</v>
       </c>
       <c r="J10" s="2">
         <f>VLOOKUP(D10,KeyCode!A:B,2,FALSE)</f>
@@ -3896,33 +3910,33 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>55</v>
+        <v>178</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>50</v>
+        <v>182</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I11" s="2" t="e">
+        <v>18</v>
+      </c>
+      <c r="I11" s="2">
         <f>VLOOKUP(C11,KeyCode!A:B,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J11" s="2" t="e">
+        <v>26</v>
+      </c>
+      <c r="J11" s="2">
         <f>VLOOKUP(D11,KeyCode!A:B,2,FALSE)</f>
-        <v>#N/A</v>
+        <v>25</v>
       </c>
       <c r="K11" s="2">
         <f>VLOOKUP(E11,KeyCode!A:B,2,FALSE)</f>
@@ -3946,29 +3960,29 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>56</v>
+        <v>179</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I12" s="2" t="e">
+        <v>18</v>
+      </c>
+      <c r="I12" s="2">
         <f>VLOOKUP(C12,KeyCode!A:B,2,FALSE)</f>
-        <v>#N/A</v>
+        <v>27</v>
       </c>
       <c r="J12" s="2">
         <f>VLOOKUP(D12,KeyCode!A:B,2,FALSE)</f>
@@ -3996,29 +4010,29 @@
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>180</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I13" s="2" t="e">
+        <v>18</v>
+      </c>
+      <c r="I13" s="2">
         <f>VLOOKUP(C13,KeyCode!A:B,2,FALSE)</f>
-        <v>#N/A</v>
+        <v>14</v>
       </c>
       <c r="J13" s="2">
         <f>VLOOKUP(D13,KeyCode!A:B,2,FALSE)</f>
@@ -4046,29 +4060,29 @@
         <v>12</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>181</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I14" s="2" t="e">
+        <v>18</v>
+      </c>
+      <c r="I14" s="2">
         <f>VLOOKUP(C14,KeyCode!A:B,2,FALSE)</f>
-        <v>#N/A</v>
+        <v>15</v>
       </c>
       <c r="J14" s="2">
         <f>VLOOKUP(D14,KeyCode!A:B,2,FALSE)</f>
@@ -4096,29 +4110,29 @@
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>6</v>
+        <v>175</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I15" s="2" t="e">
+        <v>18</v>
+      </c>
+      <c r="I15" s="2">
         <f>VLOOKUP(C15,KeyCode!A:B,2,FALSE)</f>
-        <v>#N/A</v>
+        <v>7</v>
       </c>
       <c r="J15" s="2">
         <f>VLOOKUP(D15,KeyCode!A:B,2,FALSE)</f>
@@ -4146,29 +4160,29 @@
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>50</v>
+        <v>182</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I16" s="2" t="e">
+        <v>18</v>
+      </c>
+      <c r="I16" s="2">
         <f>VLOOKUP(C16,KeyCode!A:B,2,FALSE)</f>
-        <v>#N/A</v>
+        <v>25</v>
       </c>
       <c r="J16" s="2">
         <f>VLOOKUP(D16,KeyCode!A:B,2,FALSE)</f>
@@ -4196,33 +4210,33 @@
         <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1</v>
+        <v>183</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>3</v>
+        <v>173</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I17" s="2" t="e">
+        <v>18</v>
+      </c>
+      <c r="I17" s="2">
         <f>VLOOKUP(C17,KeyCode!A:B,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J17" s="2" t="e">
+        <v>2</v>
+      </c>
+      <c r="J17" s="2">
         <f>VLOOKUP(D17,KeyCode!A:B,2,FALSE)</f>
-        <v>#N/A</v>
+        <v>4</v>
       </c>
       <c r="K17" s="2">
         <f>VLOOKUP(E17,KeyCode!A:B,2,FALSE)</f>
@@ -4246,29 +4260,29 @@
         <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>7</v>
+        <v>184</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I18" s="2" t="e">
+        <v>18</v>
+      </c>
+      <c r="I18" s="2">
         <f>VLOOKUP(C18,KeyCode!A:B,2,FALSE)</f>
-        <v>#N/A</v>
+        <v>8</v>
       </c>
       <c r="J18" s="2">
         <f>VLOOKUP(D18,KeyCode!A:B,2,FALSE)</f>
@@ -4296,29 +4310,29 @@
         <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>5</v>
+        <v>174</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I19" s="2" t="e">
+        <v>18</v>
+      </c>
+      <c r="I19" s="2">
         <f>VLOOKUP(C19,KeyCode!A:B,2,FALSE)</f>
-        <v>#N/A</v>
+        <v>6</v>
       </c>
       <c r="J19" s="2">
         <f>VLOOKUP(D19,KeyCode!A:B,2,FALSE)</f>
@@ -4340,6 +4354,10 @@
         <f>VLOOKUP(H18,KeyCode!A:B,2,FALSE)</f>
         <v>0</v>
       </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -4367,7 +4385,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="B1">
         <v>-1</v>
@@ -4375,7 +4393,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -4383,7 +4401,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -4391,7 +4409,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="B4">
         <v>2</v>

--- a/DXLibProject_Start/Data/CSV/KeyCode.xlsx
+++ b/DXLibProject_Start/Data/CSV/KeyCode.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC_User\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AE5B920-15FC-4F5F-AC84-7E2792B3AEC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F53A4B62-2EF3-4D2A-8877-31204FDC1B0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="-11490" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11835" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KeyCode" sheetId="1" r:id="rId1"/>
@@ -31,15 +31,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="191">
   <si>
     <t>GamePad</t>
   </si>
@@ -634,6 +631,13 @@
   </si>
   <si>
     <t>GP_LeftThumbLeft</t>
+  </si>
+  <si>
+    <t>BlendItem</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Gp_North</t>
   </si>
 </sst>
 </file>
@@ -684,7 +688,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -707,22 +711,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -738,9 +731,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4356,8 +4346,54 @@
       </c>
     </row>
     <row r="20" spans="1:14">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
+      <c r="A20" s="3">
+        <v>18</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I20" s="2">
+        <f>VLOOKUP(C20,KeyCode!A:B,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="J20" s="2">
+        <f>VLOOKUP(D20,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="K20" s="2">
+        <f>VLOOKUP(E20,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="L20" s="2">
+        <f>VLOOKUP(F19,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="M20" s="2">
+        <f>VLOOKUP(G19,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="N20" s="2">
+        <f>VLOOKUP(H19,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -4370,7 +4406,7 @@
           <x14:formula1>
             <xm:f>KeyCode!$A$2:$A$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:H19</xm:sqref>
+          <xm:sqref>C2:H20</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
